--- a/manuscript/3.dvm.results/diel.t.do.min.max.table.xlsx
+++ b/manuscript/3.dvm.results/diel.t.do.min.max.table.xlsx
@@ -35,19 +35,19 @@
     <t>temperature</t>
   </si>
   <si>
-    <t>do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">average minimum hyporheic </t>
-  </si>
-  <si>
-    <t>average maximum hyporheic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">average minimum epilimnetic </t>
-  </si>
-  <si>
-    <t>average maximum epilimnetic</t>
+    <t>dissolved oxygen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average minimum hyporheic </t>
+  </si>
+  <si>
+    <t>Average maximum hyporheic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average minimum epilimnetic </t>
+  </si>
+  <si>
+    <t>Average maximum epilimnetic</t>
   </si>
 </sst>
 </file>
@@ -374,7 +374,7 @@
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -442,20 +442,44 @@
       <c r="A7" t="s">
         <v>4</v>
       </c>
+      <c r="B7" s="1">
+        <v>12.1</v>
+      </c>
+      <c r="C7">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
+      <c r="B8" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="C8">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
+      <c r="B9" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="C9">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22.7</v>
+      </c>
+      <c r="C10">
+        <v>9.1999999999999993</v>
       </c>
     </row>
   </sheetData>
